--- a/resources/templates/standard/M4100-03.xlsx
+++ b/resources/templates/standard/M4100-03.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>3정 5행 평가 보고서</t>
   </si>
@@ -596,13 +599,15 @@
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -620,20 +625,20 @@
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
       <c r="AA1" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
       <c r="AD1" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE1" s="5"/>
       <c r="AF1" s="5"/>
@@ -715,7 +720,7 @@
     <row r="4" ht="20.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -733,7 +738,7 @@
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S4" s="10"/>
       <c r="T4" s="10"/>
@@ -755,7 +760,7 @@
     <row r="5" ht="20.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -773,7 +778,7 @@
       <c r="P5" s="13"/>
       <c r="Q5" s="13"/>
       <c r="R5" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S5" s="14"/>
       <c r="T5" s="14"/>
@@ -795,7 +800,7 @@
     <row r="6" ht="20.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
@@ -804,7 +809,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -824,7 +829,7 @@
       <c r="Y6" s="15"/>
       <c r="Z6" s="15"/>
       <c r="AA6" s="15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB6" s="15"/>
       <c r="AC6" s="15"/>
@@ -837,7 +842,7 @@
     <row r="7" ht="20.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -983,7 +988,7 @@
     <row r="11" ht="20.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
@@ -1129,7 +1134,7 @@
     <row r="15" ht="20.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -1275,7 +1280,7 @@
     <row r="19" ht="20.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
@@ -1421,7 +1426,7 @@
     <row r="23" ht="20.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
@@ -1567,7 +1572,7 @@
     <row r="27" ht="20.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
